--- a/2022 data/excel_outputs/236_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/236_boothwise_data.xlsx
@@ -14,798 +14,1422 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="494">
   <si>
     <t>AC 236 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>######## ######## ##### ###### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ###### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #######</t>
-  </si>
-  <si>
-    <t>######## ######## ########## #### ######## #0###</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### #0###</t>
-  </si>
-  <si>
-    <t>######## ######## #### #0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##########. #0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### #0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### ####### ## ##### #0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ########## #0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #####</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ##### .#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##########.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## #####.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## #####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####.#0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ########.##0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ########.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ### 2.#0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### ### 3.##0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### ### 3.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## #########.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### #########.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ######.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## #######.#0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #####.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###########.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###########.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ########.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ######.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ######.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### .#0###</t>
-  </si>
-  <si>
-    <t>######## ######## #### ### 1.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## #### ### 1.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## #### ### 1.### ###</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### #### ##0 9</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### #### ##0 10</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### #### ##0 ##</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### #### ##0 12</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ###### #### ##0 13</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### ######</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ## ##### #### ######.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### ####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## #########.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ## ##### #### ######.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ;####### ## #####ddh.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##########</t>
-  </si>
-  <si>
-    <t>######## ########### #### ##########.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####.##0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ######.##0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #########.##0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #########.#0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ######.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### ######.#0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #######.#0###</t>
-  </si>
-  <si>
-    <t>#### ########### ##### ##### ############.##0###</t>
-  </si>
-  <si>
-    <t>#### ########### ##### ##### ############.#0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ############.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### ############.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ############.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### #### #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ####### #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ############# ###### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ########### #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### ### ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### ## ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #### ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #### ### ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #### ## ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###.#0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###. #0 ###</t>
-  </si>
-  <si>
-    <t>##### ### ###. #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### .##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### .#0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ########## . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ###### .#### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### . ### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### ## ##### #### #######</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### . ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #####. #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #####. ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ####### #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ####### .#0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### ##### ####### .#0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ########### . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ########### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ########### . ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## ##### #### ###### #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ###### . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######### . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ;#######ddh . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ##### ###### . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ########## . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ##### #### ###### . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ### . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### . #### ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####### . #### ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## .#0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### . #### ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### . ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### ####### ##### . #### ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ########### . ### ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ########### .## ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### .##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### .#0 ###</t>
-  </si>
-  <si>
-    <t>■■■■■■■■ ■■■■■■■■ ■■■■■- ■0 ■■■C</t>
-  </si>
-  <si>
-    <t>######## ######## ##### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ########## #### ##### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### ##### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ###.1</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ###.2</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ###.3</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ###.4</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ###.5</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### #### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### . #0 ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##### #### #### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #######.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##########.##0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ########### #### #####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ################.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ## ##### #### #######.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #######.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ### 2. #0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ### 1. #0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ### 1.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ######.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ########.#0###R</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### #######.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### #######.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ## ##### #### ########.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ## ##### #### ########.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ############.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### ####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### ####.#0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #######.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #######.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ## #.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ########### #### ## #.#0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##;#ddh.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ##### ## ##### ##### ##### ## ##### #### ##;#ddh.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ## #####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ###.#0###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #####. ##0 ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #####. #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ############ #### ######## . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #############. ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #############. #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### #############. #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #### . ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ####. #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #### #### . #0 ###</t>
-  </si>
-  <si>
-    <t>### ### ##### ##### #### #### ##0 .#</t>
-  </si>
-  <si>
-    <t>### ### ##### ##### #### #### ##0 .5</t>
-  </si>
-  <si>
-    <t>######## ######## ########. #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ########### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### . ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ######. #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ##### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #######;#ddh . #0 ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### #### ####### . #0 ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ###### #### #######. #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### ####### #### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### . ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### . #0 ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #### ##### ###### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ########## #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## #### ##### #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ########### . #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ########### . ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## . ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### ##0 1</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### ##0 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### . #0 ####</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##0 ###</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ### # . #0 ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## #### ##0 ###</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####### ####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #### ##0.1</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #### ##0.2</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ###.2 #### ##0.2</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ###.2 #### ##0.3</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ### 1.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## #############.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### ####### ####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### ####### ####.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### ##### ####### ####.#0###</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ####### #### ##0.#</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #####.#0###</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ##### #### ##0.#</t>
-  </si>
-  <si>
-    <t>######## ##### ##### ##### #### ##0.9</t>
-  </si>
-  <si>
-    <t>######## ######## ## ##### ##### ###.# ###### ####### ## ###.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ## ##### ##### ###.# ###### ####### ## ###.#0###</t>
-  </si>
-  <si>
-    <t>##### ### ######## ######## ## ##### #####.#0###</t>
-  </si>
-  <si>
-    <t>###### ##### ##### ##### #### ##0.#</t>
-  </si>
-  <si>
-    <t>######## ######## ### ##### ##### ####### ######. #### ### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ### ##### ##### ####### ######. #### ### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ### ##### ##### ####### ######. #### ### 3</t>
-  </si>
-  <si>
-    <t>######## ######## ### ##### ##### ####### ######. #### ### 4</t>
-  </si>
-  <si>
-    <t>######## ######## ### ##### ##### ####### ######. #### ### 5</t>
-  </si>
-  <si>
-    <t>######## ######## ### ##### ##### ####### ######. #### ### 6</t>
-  </si>
-  <si>
-    <t>####### ########## ### #### ######## ######## ### ###### ##### #### ### 1</t>
-  </si>
-  <si>
-    <t>####### ########## ### #### ######## ######## ### ###### ##### #### ### 2</t>
-  </si>
-  <si>
-    <t>####### ########## ### #### ######## ######## ### ###### ##### #### ### 3</t>
-  </si>
-  <si>
-    <t>####### ########## ### #### ######## ######## ### ###### ##### #### ### 4</t>
-  </si>
-  <si>
-    <t>####### ########## ### #### ######## ######## ### ###### ##### #### ### 5</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ##### #### ##0.1</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ##### #### ##0.6</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ##### #### ##0.2</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ##### #### ##0.3 ### #0###</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ##### #### ##0.4 ### #0###</t>
-  </si>
-  <si>
-    <t>###### ###### ##### ##### ##### #### ##0.5</t>
-  </si>
-  <si>
-    <t>######## ######## ### ####### #####;### ###ddh.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ### ####### #####;### ###ddh.#0###</t>
-  </si>
-  <si>
-    <t>##0##0###### ##### ##### #####.#0###</t>
-  </si>
-  <si>
-    <t>### #### ######## ######## ### ####### ##### ######## ## #####.##0###</t>
-  </si>
-  <si>
-    <t>### #### ######## ######## ### ####### ##### ######## ## #####.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #########.#0###</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #########.##0###</t>
-  </si>
-  <si>
-    <t>######## ######## ######.#0### ## ####### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ######.#0### ## ###### ####</t>
-  </si>
-  <si>
-    <t>######## ######## ######### ######.#0###</t>
+    <t>ATH MAK V YALAY BALAS PAV U BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CH L MAL PAV U BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CH L MAL PI CHAMI</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY OMANAGAR M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHॉD U"TAR BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TIRAGHUMAI D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NAINI U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DHAURAHARA U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BAHARAVॉ PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BAHARAVॉ P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY B+TAKHUD.- U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY H/TA M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DEVAR M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SARU VAL U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SARU VAL I/THAT MAPH2DAR KA PARU VA D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KH3PA PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAKAR SA LAS M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY BHADED-U U0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY BHADED-U D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY JAMAUL MAJARA BHADED U -D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY ATARAUL MAPH2-D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AK7-PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AK7-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KUT -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BAR VARA-PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BAR VARA-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BAR VARA-M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY SARU SEN-PU0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY SARU SEN-M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY SARU SEN-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAJA.PARU -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY HAR SHANAPARU MAJARA MAJA.PARU - M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY VIRAGHUMAI SAK U 7-U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY VIRAGHUMAI SAK U 7-D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY L MAYAR -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GADAUL -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAMASIBAJ U UG-. M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BAS:TAPARU -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DARASEDA-PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DARASEDA-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BASAHAR-M0BHAG</t>
+  </si>
+  <si>
+    <t>DYASHRATHABH KDYASHRCH J SDYAIDYAS BBHDYAIL|SHRCH|THABHDYABBH|CHNK0JBH|THABHDYAS</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY &lt;YAUHARA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SADH=L -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHANAPARU -M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY ACHA. BARETH@-PU0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY ACHA. BARETH@-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY ACHA. -M0BHAG</t>
+  </si>
+  <si>
+    <t>NAVIN ATH MAK V YALAY AUDAHA-PU0BHAG</t>
+  </si>
+  <si>
+    <t>NAVIN ATH MAK V YALAY AUDAHA-P0BHAG</t>
+  </si>
+  <si>
+    <t>NAVIN A0 V0 AUDAHA-HAL MAB</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAI PARU VA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PANAUT -M0BHAG</t>
+  </si>
+  <si>
+    <t>SARADHAV U A IDTAR KALEJ SARADHAV U A KAMARA NAM0 9</t>
+  </si>
+  <si>
+    <t>SARADHAV U A IDTAR KALEJ SARADHAV U A KAMARA NAM0 10</t>
+  </si>
+  <si>
+    <t>SARADHAV U A IDTAR KALEJ SARADHAV U A KAMARA NAM0 11</t>
+  </si>
+  <si>
+    <t>SARADHAV U A IDTAR KALEJ SARADHAV U A KAMARA NAM0 12</t>
+  </si>
+  <si>
+    <t>SARADHAV U A IDTAR KALEJ SARADHAV U A KAMARA NAM0 13</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GAR BADAS KA PARU VA MAJARA SARADHAVU A-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHATAR -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SARU JAVA PARU VA MAJARA BHATAR - M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KUSEL -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAHUVॉGAMV-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY U"TAMAPARU MAJARA MAHUVॉGAMV- M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KANAKOTA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY UDAGHATA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAYAPARU -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GTAVAR KA PARU VA MAJARA RAYAPARU - M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BERAUR-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY HALAD KA PARU VA MAJARA BERAUR- U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CH L RAKAS</t>
+  </si>
+  <si>
+    <t>ATH MAK PADDEPARU VA MAJARA CH L RAKAS-PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KALAV LAYA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PATANAKHALASA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAMAPAHU RAYA AIVAL-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PATAVAHRAYA SANI-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DUDAUL -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHANAHAT-M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY MOHARAVॉ-PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TERAKHUD.-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHAJH -M0BHAG</t>
+  </si>
+  <si>
+    <t>K:YA PAV U . MA4Y MAK V YALAY AJU.NAPARU -PU0BHAG</t>
+  </si>
+  <si>
+    <t>K:YA PAV U . MA4Y MAK V YALAY AJU.NAPARU -P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY JAMAKHAL-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SA LAGAPARU -M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY SAGAVARA-PU0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY SAGAVARA-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GADAHRAYAN PARU VA MAJARA SAGAVARA- M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY LOHADA-PU0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY LOHADA-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NONAR-M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY NONAR I/THAT DOL PARU VA- PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY S4DAPARU -M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY PAPARODAR-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PATHARAMANI-M0BHAG</t>
+  </si>
+  <si>
+    <t>LI PALE VARANATH IDTAR KALEJ PAHADIBAJ U UG-. PU0BHAG</t>
+  </si>
+  <si>
+    <t>LI PALE VARANATH IDTAR KALEJ PAHADIBAJ U UG-. P0BHAG</t>
+  </si>
+  <si>
+    <t>LI PALE VARANATH IDTAR KALEJ PAHADIBAJ U UG-. M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY PAHADIBAJ U UG-. D0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY PAHADIBAJ U UG-. U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAHARAJAPARU MAJARA PAHADIBAJ U UG-. M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY OVAR MAJARA PAHADIBAJ U UG-. M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KUCHARAM-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAKAR SANI-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KॉT -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY HARA.-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHAURA-PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHAURA-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DAHAHRAYA PARU VA MAJARA CHAURA M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KALAVARA BAJ U UG. M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KALAVARABAJ U UG. DAMNN BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KALAVARAKHUD. M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHEHRAYA M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DEVAL PI CHAM BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AGARAHUDDA M4Y BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY NAHARA M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAMAPARU M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY ORA-U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY ORA- D0 BHAG</t>
+  </si>
+  <si>
+    <t>SAMKUL BHAVAN ORA- D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAKARAUL -M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAIPARU - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KOHAR M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KAHETAMAPH2 PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KAHETAMAPH2 - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PAKTAYAJAPTI - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHAIR MAJARA SAKARAUL -M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PARAS=JA - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PARAS=JA - D0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY PARAS=JA - U0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY PARAS=JA - D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PACHOKHAR PU0 BHAG</t>
+  </si>
+  <si>
+    <t>DYASHRATHABH KDYASHRCH J SDYAIDYAS K|L|AIBHT|THABHDYASDYAJ N K4S JBH|THABHDYAS</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY ASHOH - PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY ASHOH - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY ITAURA- P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BABAP U RU PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHARASEDA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KAPANA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY JAHRAHA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NॉD - PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NॉD - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAURA PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAURA P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAKAHRAYA M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY B+TA BAJ U UG. U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY B+TA BAJ U UG. -D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MIU /LAM PARU VA MAJARA B+TA BAJ U UG. -M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BACHARAN P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BACHARAN - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY U:NAYABANA. - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GANIVA SARPARU - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAMAPAHU RAYA MAJARA HARADAUL M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY ANIPARU - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY HARADAUL - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DAKDHAYA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY K:DHAVAGNAYA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AKHARA M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAGARAHAI - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BॉDHA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GAUHANIKALॉ - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY GAUHANIKALॉ I/THAT GADHAVARA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHAJ U AUL MAPH2 - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DEHAJCHAMAPH2 - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BADHAVARA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DEVAKAL - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY JAMAKHAL - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PAIKORAMAPH2 - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY B SALA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DAHRAYA PARU VA MAJARA ATARAUL - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KUI - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY &lt;YASAB:NA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BALAPARU KHALASA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BADH U A - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KAMTH@PARU - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY KAMTH@PARU - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KALAP U RU - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY CHAK=DH - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHARAKURA. -U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHAI U HAR MAPH2 - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY ITARAUR - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHAKAJAPHAR-M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY RAGAUL - U0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY RAGAUL - D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHE CHAHRAYA KHUD. - PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHE CHAHRAHA KHUD. - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AN:DAPARU MAJARA CHE CHAHRAYA KHUD. - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>NAVIN ATH MAK V YALAY LAUKDHAYAKHUD. - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAPAHA -M0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY KASAHAI THAM - U0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY KASAHAI THAM - D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KASAHAI THAM - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KAMU JANAPARU VA MAJARA KASAHAI - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KAMU JANAPARU VA MAJARA KASAHAI - D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NAIDAGU NAYA MAJARA KASAHAI - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BANAVAR PARU - M0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY BANAKAT U0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY BANAKAT D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BANAKAT PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BANAKAT P0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY B:DHAI U N - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY LODHAVARA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY LODHAVARA - M4Y BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GCHAPANI BAHAR KHEDA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAVARA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHAJUHRAHA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KADIKHEDA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SABHAPARU TARॉV - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAUVANI - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SHITALAPARU KONAHAS - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DAB U AR -M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY REHUTA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY REHUTA - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHABHAUR - D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY USAR PARU VA MAJARA BHABHAUR - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAKAR PALADEV - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CH L MAPH2 - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AIRANAMAPH2-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAMAYAPARU -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHANAUTAMAPH2-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY VIRA-M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY ITAKHAR -PU0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY ITAKHAR -P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KADARAGAMJ-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAMAPH2-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GADH GHAT-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DOMANAKHERA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DAKHANI-M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY KHUMANIPARU VA MAJARA DAKHANI- M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PAHADIBAJ U UGAS . ANI-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAHADEV KA PARU VA MAJARA BHAIS=DHA- M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY VAMSHIPARU MAJARA BHAIS=DHA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHAIS=DHA BHAG 1- M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHAIS=DHA BHAG 2- P0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY BHAIS=DHA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BAGALAI-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GOPALAPARU -M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY PARU VA TAR=HA-U0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY PARU VA TAR=HA-D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CH:YGAHANA-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NARAYANAPARU -D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AMANAPARU -U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TE HRAYA PARU VA MAJARA AMANAPARU - P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHAMBHAI-U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AHAMADAGAMJ-D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PADAR MAPH2-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHAKALAGAJ U BABA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY K LA-U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAI PARU VAMAPH2-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PATHARAUDI-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TARॉV-U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TARॉV-D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BAIHAR-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DAKDHAYA MAJARA PAHARA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BIHAR MAJARA PAHARA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SEHARA MAJARA PAHARA-M0BHAG</t>
+  </si>
+  <si>
+    <t>NAVIN ATH MAK V YALAY PAHARA-M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY PAHARA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHISHAMAPARU -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GOBAHRAYA BAJ U UG-. M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KTAKTAHARA-PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KTAKTAHARA-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAU B-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DAJ U .NAPARU VA MAJARA MAU B-M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY MAU(B)-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KAREDI KA PARU VA I/THAT AMANAR KA PARU VA MAJARA MAU(B)-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KARAR -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DHAURAH MAPH2-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHAK BHATAURA-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY LAK U -M0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY PATODA- M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY A M LAHA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAKU DANAPARU - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PADDEYAPARU VA MAJARA SAKU DANAPARU - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAUL K YANAPARU - PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAUL K YANAPARU - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GADAHRAYAN PARU VA MAJARA RAUL K YANAPARU - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MAHADEVAN MAJARA R SAN - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BH\DAHAI MAJARA R SAN - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAMARAR MAJARA R SAN - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GAUSHALA MAJARA R SAN- M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY PHATAPARU VA MAJARA R SAN - M0 BHAG</t>
+  </si>
+  <si>
+    <t>RATAN NATH IDTAR KALEJ R SAN KAN SAM0 -4</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHAGAVATAPARU - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KOL=HA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHAVANIPARU - M0 BHAG</t>
+  </si>
+  <si>
+    <t>DYASHRATHABH KDYASHRCH J SDYAIDYAS SHRCH|THABHETHABHDYATHABHJDYASDY NCH0 JBH|THABHDYAS</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KO HUAMAPH2 - D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MANAPARU - PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY B:DAR - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GHARU ETANAPARU - D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GHARU ETANAPARU - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SARAKHOR - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY DHOLABAJA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY MAK U U :DAPARU - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY HAHRAHARAPARU - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHARAI HA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY DAG U VA - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RAMAPARU PALADEV- M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GODA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GODA - D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY VIDARAPARU VA MAJARA GODA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY KORAR MAJARA G3DA - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY AKABARAPARU (B) - M0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY BHARATAKUP MAJARA AKABARAPARU (B) - D0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY BHARATAKUP MAJARA AKABARAPARU (B) - U0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHAPAKTAHA MAJARA BHARATAPARU TARॉV - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHARATAPARU TARॉV - PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHARATAPARU TARॉV - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SABHAPARU I/THAT BARACH - M0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY BARACH I/THAT SABHAPARU - M0 BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY MAINAHAIMAPH2 M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BAUNA PARU VA M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SEMAHRAYA JAG:NATHAVASI - M0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHAGANAPARU - D0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BALAPARU MAPH2 - PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY B:DARAKOL - PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHAPARAMAPH2 KAN SAM0 1</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHAPARAMAPH2 KAN SAM0 2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY THAR^ - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BHARATHAUL P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BAHARA PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAGADAHA PARU VA MAJARA BAHARA - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHOH - P0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHOH PU0 BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SAM`AMAPARU -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY BARAMAPARU -M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RANIPARU KHAK2-D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MACHAHRAHA-U0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY SHAVARAMAPARU KAN SAM0-1</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY SHAVARAMAPARU KAN SAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SHAVARAMAPARU BHAG-2 KAN SAM0-2</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SHAVARAMAPARU BHAG-2 KAN SAM0-3</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SONARAN PARU VA MAJARA SHAVARAMAPARU -D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KHUTAHA-D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY RANIPARU BHAM.M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHATARAGOKULAPARU -U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY CHATARAGOKULAPARU -D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY MANOHARAGAMJ MAJARA SITAPARU JRAL-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KUSHAVAHA B/TI SITAPARU JRAL- PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KUSHAVAHA B/TI SITAPARU JRAL- P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KATARAGAD U R-M0BHAG</t>
+  </si>
+  <si>
+    <t>POBAR IDTAR KALEJ KAN SAM0-1</t>
+  </si>
+  <si>
+    <t>POBAR IDTAR KALEJ KAN SAM0-2</t>
+  </si>
+  <si>
+    <t>POBAR IDTAR KALEJ KAN SAM0-3</t>
+  </si>
+  <si>
+    <t>POBAR IDTAR KALEJ KAN SAM0-4</t>
+  </si>
+  <si>
+    <t>POBAR IDTAR KALEJ KAN SAM0-5</t>
+  </si>
+  <si>
+    <t>POBAR IDTAR KALEJ KAN SAM0-6</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SITAPARU THAM-M0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY \DALAURA-U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY \DALAURA-D0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY GADH VA-P0BHAG</t>
+  </si>
+  <si>
+    <t>CHAGKUT IDTAR KALEJ KAV KAN SAM0-8</t>
+  </si>
+  <si>
+    <t>CHAGKUT IDTAR KALEJ KAV KAN SAM0-7</t>
+  </si>
+  <si>
+    <t>CHAGKUT IDTAR KALEJ KAV KAN SAM0-6</t>
+  </si>
+  <si>
+    <t>CHAGKUT IDTAR KALEJ KAV KAN SAM0-5</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NAI BAJAR KAV BHAG-1 B DAU MAMI:DAR KE PAS-PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NAI BAJAR KAV BHAG-1 B DAU MAMI:DAR KE PAS-P0BHAG</t>
+  </si>
+  <si>
+    <t>SAMKUL BHAVAN ATH MAK V YALAY NAI BAJAR KAV - M0BHAG</t>
+  </si>
+  <si>
+    <t>JANASEVA IDTAR KALEJ KAV KAN SAM0-1</t>
+  </si>
+  <si>
+    <t>JANASEVA IDTAR KALEJ KAV KAN SAM0-5</t>
+  </si>
+  <si>
+    <t>JANASEVA IDTAR KALEJ KAV KAN SAM0-2</t>
+  </si>
+  <si>
+    <t>JANASEVA IDTAR KALEJ KAV KAN SAM0-3</t>
+  </si>
+  <si>
+    <t>JANASEVA IDTAR KALEJ KAV KAN SAM0-4</t>
+  </si>
+  <si>
+    <t>PAV U N MA4Y MAK BA LAKA V YALAY NAYA BAJAR KAV RAAPHAK CHAURAHA.PU0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U N MA4Y MAK BA LAKA V YALAY NAYA BAJAR KAV RAAPHAK CHAURAHAAL MATH</t>
+  </si>
+  <si>
+    <t>PAV U N MA4Y MAK BA LAKA V YALAY NAYA BAJAR KAV RAAPHAK CHAURAHA.P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NAYA BAJAR KAV BHAG.2 RAAPHAK CHAURAHA.PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NAYA BAJAR KAV BHAG.2 RAAPHAK CHAURAHA.P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY NAYA BAJAR KAV BHAG.2 RAAPHAK CHAURAHA.D0BHAG</t>
+  </si>
+  <si>
+    <t>SATI ANAS U I U YA ATH MAK V YALAY NAGAR NEG KAV - D0BHAG</t>
+  </si>
+  <si>
+    <t>SATI ANAS U I U YA ATH MAK V YALAY NAGAR NEG KAV - M0BHAG</t>
+  </si>
+  <si>
+    <t>SATI ANAS U I U YA ATH MAK V YALAY NAGAR NEG KAV - U0BHAG</t>
+  </si>
+  <si>
+    <t>RAJ SH. PAJ U SHO"TAM DAS TAM DAN ULCH ATH MAK V YALAY NAGAR PA LAKA KAV -PU0BHAG</t>
+  </si>
+  <si>
+    <t>RAJ SH. PAJ U SHO"TAM DAS TAM DAN ULCH ATH MAK V YALAY NAGAR PA LAKA KAV -P0BHAG</t>
+  </si>
+  <si>
+    <t>RAJAK2Y BA LAKA IDTAR KALEJ KAV KAN SAM0-1</t>
+  </si>
+  <si>
+    <t>RAJAK2Y BA LAKA IDTAR KALEJ KAV KAN SAM0-2</t>
+  </si>
+  <si>
+    <t>RAJAK2Y BA LAKA IDTAR KALEJ KAV KAN SAM0-3 HAL U0BHAG</t>
+  </si>
+  <si>
+    <t>RAJAK2Y BA LAKA IDTAR KALEJ KAV KAN SAM0-4 HAL D0BHAG</t>
+  </si>
+  <si>
+    <t>RAJAK2Y BA LAKA IDTAR KALEJ KAV KAN SAM0-5</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY NAGAR NEG KAV (SADAR ROD)- PU0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY NAGAR NEG KAV (SADAR ROD)- P0BHAG</t>
+  </si>
+  <si>
+    <t>JE0EM0BA LAKA IDTAR KALEJ KAV -D0BHAG</t>
+  </si>
+  <si>
+    <t>JE0EM0BA LAKA IDTAR KALEJ KAV -M0BHAG</t>
+  </si>
+  <si>
+    <t>JE0EM0BA LAKA IDTAR KALEJ KAV -U0BHAG</t>
+  </si>
+  <si>
+    <t>SATI SITA ATH MAK V YALAY NAGAR NEG KAV SHOBHA SAMH KA PARU VA-PU0BHAG</t>
+  </si>
+  <si>
+    <t>SATI SITA ATH MAK V YALAY NAGAR NEG KAV SHOBHA SAMH KA PARU VA-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KAV MAPH2-PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY SONEPARU MAJARA KAV MAPH2-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KAPASETH@-D0BHAG KA PI CHAMI KAN</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY KAPASETH@-D0BHAG KA PAV U KAN</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY I/LA MAYॉ /KUL TAR=HA-U0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY I/LA MAYॉ /KUL TAR=HA-D0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY TAR=HA-P0BHAG</t>
+  </si>
+  <si>
+    <t>PAV U . MA4Y MAK V YALAY TAR=HA-PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-PU0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 430</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 431</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 432</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 433</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 434</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 435</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 436</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 437</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 438</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 439</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 440</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 441</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 442</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 443</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 444</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 445</t>
+  </si>
+  <si>
+    <t>ATH MAK V YALAY TAR=HA-P0BHAG ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 446</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -878,8 +1502,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -895,7 +1527,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -903,12 +1535,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1207,82 +1857,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>264</v>
+        <v>472</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>473</v>
       </c>
       <c r="E2" t="s">
-        <v>266</v>
+        <v>474</v>
       </c>
       <c r="F2" t="s">
-        <v>267</v>
+        <v>475</v>
       </c>
       <c r="G2" t="s">
-        <v>268</v>
+        <v>476</v>
       </c>
       <c r="H2" t="s">
-        <v>269</v>
+        <v>477</v>
       </c>
       <c r="I2" t="s">
-        <v>270</v>
+        <v>478</v>
       </c>
       <c r="J2" t="s">
-        <v>271</v>
+        <v>479</v>
       </c>
       <c r="K2" t="s">
-        <v>272</v>
+        <v>480</v>
       </c>
       <c r="L2" t="s">
-        <v>273</v>
+        <v>481</v>
       </c>
       <c r="M2" t="s">
-        <v>274</v>
+        <v>482</v>
       </c>
       <c r="N2" t="s">
-        <v>275</v>
+        <v>483</v>
       </c>
       <c r="O2" t="s">
-        <v>276</v>
+        <v>484</v>
       </c>
       <c r="P2" t="s">
-        <v>277</v>
+        <v>485</v>
       </c>
       <c r="Q2" t="s">
-        <v>278</v>
+        <v>486</v>
       </c>
       <c r="R2" t="s">
-        <v>279</v>
+        <v>487</v>
       </c>
       <c r="S2" t="s">
-        <v>280</v>
+        <v>488</v>
       </c>
       <c r="T2" t="s">
-        <v>281</v>
+        <v>489</v>
       </c>
       <c r="U2" t="s">
-        <v>282</v>
+        <v>490</v>
       </c>
       <c r="V2" t="s">
-        <v>283</v>
+        <v>491</v>
       </c>
       <c r="W2" t="s">
-        <v>284</v>
+        <v>492</v>
       </c>
       <c r="X2" t="s">
-        <v>285</v>
+        <v>493</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1290,7 +2009,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>876</v>
@@ -1364,7 +2083,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>1154</v>
@@ -1438,7 +2157,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>798</v>
@@ -1512,7 +2231,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>934</v>
@@ -1586,7 +2305,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C7">
         <v>410</v>
@@ -1660,7 +2379,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C8">
         <v>1124</v>
@@ -1734,7 +2453,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C9">
         <v>1129</v>
@@ -1808,7 +2527,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="C10">
         <v>895</v>
@@ -1882,7 +2601,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C11">
         <v>632</v>
@@ -1956,7 +2675,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="C12">
         <v>842</v>
@@ -2030,7 +2749,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C13">
         <v>801</v>
@@ -2104,7 +2823,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>912</v>
@@ -2178,7 +2897,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C15">
         <v>369</v>
@@ -2252,7 +2971,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>828</v>
@@ -2326,7 +3045,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C17">
         <v>1093</v>
@@ -2400,7 +3119,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C18">
         <v>1108</v>
@@ -2474,7 +3193,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C19">
         <v>992</v>
@@ -2548,7 +3267,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C20">
         <v>654</v>
@@ -2622,7 +3341,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C21">
         <v>714</v>
@@ -2696,7 +3415,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <v>453</v>
@@ -2770,7 +3489,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C23">
         <v>706</v>
@@ -2844,7 +3563,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C24">
         <v>923</v>
@@ -2918,7 +3637,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>934</v>
@@ -2992,7 +3711,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C26">
         <v>649</v>
@@ -3066,7 +3785,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C27">
         <v>1218</v>
@@ -3140,7 +3859,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>1076</v>
@@ -3214,7 +3933,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>902</v>
@@ -3288,7 +4007,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>703</v>
@@ -3362,7 +4081,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>1075</v>
@@ -3436,7 +4155,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>993</v>
@@ -3510,7 +4229,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>993</v>
@@ -3584,7 +4303,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>1092</v>
@@ -3658,7 +4377,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>691</v>
@@ -3732,7 +4451,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>805</v>
@@ -3806,7 +4525,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>685</v>
@@ -3880,7 +4599,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>550</v>
@@ -3954,7 +4673,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>869</v>
@@ -4028,7 +4747,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>1010</v>
@@ -4102,7 +4821,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>1125</v>
@@ -4176,7 +4895,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>767</v>
@@ -4250,7 +4969,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>826</v>
@@ -4324,7 +5043,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>700</v>
@@ -4398,7 +5117,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>749</v>
@@ -4472,7 +5191,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>242</v>
@@ -4546,7 +5265,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>1170</v>
@@ -4620,7 +5339,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>1192</v>
@@ -4694,7 +5413,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="C49">
         <v>744</v>
@@ -4768,7 +5487,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="C50">
         <v>774</v>
@@ -4842,7 +5561,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>985</v>
@@ -4916,7 +5635,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C52">
         <v>454</v>
@@ -4990,7 +5709,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>843</v>
@@ -5064,7 +5783,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>1072</v>
@@ -5138,7 +5857,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="C55">
         <v>929</v>
@@ -5212,7 +5931,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>545</v>
@@ -5286,7 +6005,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="C57">
         <v>943</v>
@@ -5360,7 +6079,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="C58">
         <v>772</v>
@@ -5434,7 +6153,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="C59">
         <v>753</v>
@@ -5508,7 +6227,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="C60">
         <v>471</v>
@@ -5582,7 +6301,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="C61">
         <v>833</v>
@@ -5656,7 +6375,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="C62">
         <v>782</v>
@@ -5730,7 +6449,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="C63">
         <v>1139</v>
@@ -5804,7 +6523,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="C64">
         <v>1104</v>
@@ -5878,7 +6597,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>1101</v>
@@ -5952,7 +6671,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C66">
         <v>782</v>
@@ -6026,7 +6745,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>420</v>
@@ -6100,7 +6819,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="C68">
         <v>875</v>
@@ -6174,7 +6893,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="C69">
         <v>612</v>
@@ -6248,7 +6967,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="C70">
         <v>578</v>
@@ -6322,7 +7041,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>52</v>
+        <v>94</v>
       </c>
       <c r="C71">
         <v>827</v>
@@ -6396,7 +7115,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>897</v>
@@ -6470,7 +7189,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>736</v>
@@ -6544,7 +7263,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="C74">
         <v>749</v>
@@ -6618,7 +7337,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="C75">
         <v>592</v>
@@ -6692,7 +7411,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>951</v>
@@ -6766,7 +7485,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>570</v>
@@ -6840,7 +7559,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>1117</v>
@@ -6914,7 +7633,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>54</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>683</v>
@@ -6988,7 +7707,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="C80">
         <v>758</v>
@@ -7062,7 +7781,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>56</v>
+        <v>104</v>
       </c>
       <c r="C81">
         <v>746</v>
@@ -7136,7 +7855,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>899</v>
@@ -7210,7 +7929,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C83">
         <v>568</v>
@@ -7284,7 +8003,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>858</v>
@@ -7358,7 +8077,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="C85">
         <v>769</v>
@@ -7432,7 +8151,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="C86">
         <v>704</v>
@@ -7506,7 +8225,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="C87">
         <v>630</v>
@@ -7580,7 +8299,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
       <c r="C88">
         <v>562</v>
@@ -7654,7 +8373,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C89">
         <v>647</v>
@@ -7728,7 +8447,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>25</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>625</v>
@@ -7802,7 +8521,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="C91">
         <v>851</v>
@@ -7876,7 +8595,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>31</v>
+        <v>115</v>
       </c>
       <c r="C92">
         <v>411</v>
@@ -7950,7 +8669,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="C93">
         <v>563</v>
@@ -8024,7 +8743,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>63</v>
+        <v>117</v>
       </c>
       <c r="C94">
         <v>1183</v>
@@ -8098,7 +8817,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>64</v>
+        <v>118</v>
       </c>
       <c r="C95">
         <v>486</v>
@@ -8172,7 +8891,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="C96">
         <v>997</v>
@@ -8246,7 +8965,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>27</v>
+        <v>120</v>
       </c>
       <c r="C97">
         <v>836</v>
@@ -8320,7 +9039,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>62</v>
+        <v>121</v>
       </c>
       <c r="C98">
         <v>862</v>
@@ -8394,7 +9113,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="C99">
         <v>698</v>
@@ -8468,7 +9187,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>266</v>
@@ -8542,7 +9261,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="C101">
         <v>1175</v>
@@ -8616,7 +9335,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="C102">
         <v>1189</v>
@@ -8690,7 +9409,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="C103">
         <v>1239</v>
@@ -8764,7 +9483,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>35</v>
+        <v>127</v>
       </c>
       <c r="C104">
         <v>780</v>
@@ -8838,7 +9557,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="C105">
         <v>662</v>
@@ -8912,7 +9631,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>36</v>
+        <v>129</v>
       </c>
       <c r="C106">
         <v>667</v>
@@ -8986,7 +9705,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="C107">
         <v>536</v>
@@ -9060,7 +9779,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="C108">
         <v>958</v>
@@ -9134,7 +9853,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="C109">
         <v>1177</v>
@@ -9208,7 +9927,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="C110">
         <v>1103</v>
@@ -9282,7 +10001,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="C111">
         <v>1102</v>
@@ -9356,7 +10075,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="C112">
         <v>691</v>
@@ -9430,7 +10149,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
       <c r="C113">
         <v>554</v>
@@ -9504,7 +10223,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>71</v>
+        <v>137</v>
       </c>
       <c r="C114">
         <v>626</v>
@@ -9578,7 +10297,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="C115">
         <v>359</v>
@@ -9652,7 +10371,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="C116">
         <v>690</v>
@@ -9726,7 +10445,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="C117">
         <v>697</v>
@@ -9800,7 +10519,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
       <c r="C118">
         <v>712</v>
@@ -9874,7 +10593,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="C119">
         <v>523</v>
@@ -9948,7 +10667,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="C120">
         <v>465</v>
@@ -10022,7 +10741,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>61</v>
+        <v>144</v>
       </c>
       <c r="C121">
         <v>939</v>
@@ -10096,7 +10815,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="C122">
         <v>891</v>
@@ -10170,7 +10889,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="C123">
         <v>1233</v>
@@ -10244,7 +10963,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="C124">
         <v>1099</v>
@@ -10318,7 +11037,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="C125">
         <v>821</v>
@@ -10392,7 +11111,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>76</v>
+        <v>149</v>
       </c>
       <c r="C126">
         <v>935</v>
@@ -10466,7 +11185,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="C127">
         <v>524</v>
@@ -10540,7 +11259,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>636</v>
@@ -10614,7 +11333,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="C129">
         <v>705</v>
@@ -10688,7 +11407,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="C130">
         <v>550</v>
@@ -10762,7 +11481,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="C131">
         <v>627</v>
@@ -10836,7 +11555,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="C132">
         <v>721</v>
@@ -10910,7 +11629,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>368</v>
@@ -10984,7 +11703,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>1185</v>
@@ -11058,7 +11777,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>84</v>
+        <v>158</v>
       </c>
       <c r="C135">
         <v>1088</v>
@@ -11132,7 +11851,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>85</v>
+        <v>159</v>
       </c>
       <c r="C136">
         <v>1145</v>
@@ -11206,7 +11925,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="C137">
         <v>785</v>
@@ -11280,7 +11999,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
       <c r="C138">
         <v>834</v>
@@ -11354,7 +12073,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>88</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>1211</v>
@@ -11428,7 +12147,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>77</v>
+        <v>163</v>
       </c>
       <c r="C140">
         <v>874</v>
@@ -11502,7 +12221,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="C141">
         <v>345</v>
@@ -11576,7 +12295,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="C142">
         <v>887</v>
@@ -11650,7 +12369,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="C143">
         <v>614</v>
@@ -11724,7 +12443,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="C144">
         <v>431</v>
@@ -11798,7 +12517,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="C145">
         <v>913</v>
@@ -11872,7 +12591,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="C146">
         <v>811</v>
@@ -11946,7 +12665,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="C147">
         <v>977</v>
@@ -12020,7 +12739,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>94</v>
+        <v>171</v>
       </c>
       <c r="C148">
         <v>956</v>
@@ -12094,7 +12813,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>95</v>
+        <v>172</v>
       </c>
       <c r="C149">
         <v>357</v>
@@ -12168,7 +12887,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>96</v>
+        <v>173</v>
       </c>
       <c r="C150">
         <v>1200</v>
@@ -12242,7 +12961,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="C151">
         <v>549</v>
@@ -12316,7 +13035,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="C152">
         <v>844</v>
@@ -12390,7 +13109,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>98</v>
+        <v>176</v>
       </c>
       <c r="C153">
         <v>837</v>
@@ -12464,7 +13183,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>98</v>
+        <v>177</v>
       </c>
       <c r="C154">
         <v>871</v>
@@ -12538,7 +13257,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>99</v>
+        <v>178</v>
       </c>
       <c r="C155">
         <v>695</v>
@@ -12612,7 +13331,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>100</v>
+        <v>179</v>
       </c>
       <c r="C156">
         <v>668</v>
@@ -12686,7 +13405,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>101</v>
+        <v>180</v>
       </c>
       <c r="C157">
         <v>693</v>
@@ -12760,7 +13479,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>102</v>
+        <v>181</v>
       </c>
       <c r="C158">
         <v>690</v>
@@ -12834,7 +13553,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
       <c r="C159">
         <v>1004</v>
@@ -12908,7 +13627,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="C160">
         <v>629</v>
@@ -12982,7 +13701,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>104</v>
+        <v>184</v>
       </c>
       <c r="C161">
         <v>615</v>
@@ -13056,7 +13775,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="C162">
         <v>1112</v>
@@ -13130,7 +13849,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="C163">
         <v>498</v>
@@ -13204,7 +13923,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>98</v>
+        <v>187</v>
       </c>
       <c r="C164">
         <v>915</v>
@@ -13278,7 +13997,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>105</v>
+        <v>188</v>
       </c>
       <c r="C165">
         <v>1179</v>
@@ -13352,7 +14071,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="C166">
         <v>441</v>
@@ -13426,7 +14145,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="C167">
         <v>622</v>
@@ -13500,7 +14219,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="C168">
         <v>683</v>
@@ -13574,7 +14293,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>109</v>
+        <v>192</v>
       </c>
       <c r="C169">
         <v>809</v>
@@ -13648,7 +14367,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="C170">
         <v>392</v>
@@ -13722,7 +14441,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="C171">
         <v>1077</v>
@@ -13796,7 +14515,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>98</v>
+        <v>195</v>
       </c>
       <c r="C172">
         <v>1105</v>
@@ -13870,7 +14589,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="C173">
         <v>1029</v>
@@ -13944,7 +14663,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>112</v>
+        <v>197</v>
       </c>
       <c r="C174">
         <v>833</v>
@@ -14018,7 +14737,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>113</v>
+        <v>198</v>
       </c>
       <c r="C175">
         <v>581</v>
@@ -14092,7 +14811,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>114</v>
+        <v>199</v>
       </c>
       <c r="C176">
         <v>664</v>
@@ -14166,7 +14885,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>115</v>
+        <v>200</v>
       </c>
       <c r="C177">
         <v>558</v>
@@ -14240,7 +14959,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="C178">
         <v>1093</v>
@@ -14314,7 +15033,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>104</v>
+        <v>202</v>
       </c>
       <c r="C179">
         <v>760</v>
@@ -14388,7 +15107,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>116</v>
+        <v>203</v>
       </c>
       <c r="C180">
         <v>1065</v>
@@ -14462,7 +15181,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>117</v>
+        <v>204</v>
       </c>
       <c r="C181">
         <v>764</v>
@@ -14536,7 +15255,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="C182">
         <v>491</v>
@@ -14610,7 +15329,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>103</v>
+        <v>206</v>
       </c>
       <c r="C183">
         <v>498</v>
@@ -14684,7 +15403,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>116</v>
+        <v>207</v>
       </c>
       <c r="C184">
         <v>1184</v>
@@ -14758,7 +15477,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>119</v>
+        <v>208</v>
       </c>
       <c r="C185">
         <v>939</v>
@@ -14832,7 +15551,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>91</v>
+        <v>209</v>
       </c>
       <c r="C186">
         <v>621</v>
@@ -14906,7 +15625,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>120</v>
+        <v>210</v>
       </c>
       <c r="C187">
         <v>749</v>
@@ -14980,7 +15699,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>88</v>
+        <v>211</v>
       </c>
       <c r="C188">
         <v>683</v>
@@ -15054,7 +15773,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>88</v>
+        <v>212</v>
       </c>
       <c r="C189">
         <v>967</v>
@@ -15128,7 +15847,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>88</v>
+        <v>213</v>
       </c>
       <c r="C190">
         <v>512</v>
@@ -15202,7 +15921,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>91</v>
+        <v>214</v>
       </c>
       <c r="C191">
         <v>537</v>
@@ -15276,7 +15995,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>104</v>
+        <v>215</v>
       </c>
       <c r="C192">
         <v>1182</v>
@@ -15350,7 +16069,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>121</v>
+        <v>216</v>
       </c>
       <c r="C193">
         <v>1198</v>
@@ -15424,7 +16143,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>122</v>
+        <v>217</v>
       </c>
       <c r="C194">
         <v>1187</v>
@@ -15498,7 +16217,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>91</v>
+        <v>218</v>
       </c>
       <c r="C195">
         <v>433</v>
@@ -15572,7 +16291,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>123</v>
+        <v>219</v>
       </c>
       <c r="C196">
         <v>829</v>
@@ -15646,7 +16365,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>98</v>
+        <v>220</v>
       </c>
       <c r="C197">
         <v>687</v>
@@ -15720,7 +16439,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>97</v>
+        <v>221</v>
       </c>
       <c r="C198">
         <v>570</v>
@@ -15794,7 +16513,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>124</v>
+        <v>222</v>
       </c>
       <c r="C199">
         <v>1014</v>
@@ -15868,7 +16587,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>125</v>
+        <v>223</v>
       </c>
       <c r="C200">
         <v>420</v>
@@ -15942,7 +16661,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="C201">
         <v>306</v>
@@ -16016,7 +16735,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
       <c r="C202">
         <v>1151</v>
@@ -16090,7 +16809,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>126</v>
+        <v>226</v>
       </c>
       <c r="C203">
         <v>836</v>
@@ -16164,7 +16883,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>127</v>
+        <v>227</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -16238,7 +16957,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>104</v>
+        <v>228</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -16312,7 +17031,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>40</v>
+        <v>229</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -16386,7 +17105,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>128</v>
+        <v>230</v>
       </c>
       <c r="C207">
         <v>966</v>
@@ -16460,7 +17179,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>128</v>
+        <v>231</v>
       </c>
       <c r="C208">
         <v>843</v>
@@ -16534,7 +17253,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>129</v>
+        <v>232</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -16608,7 +17327,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>130</v>
+        <v>233</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -16682,7 +17401,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>131</v>
+        <v>234</v>
       </c>
       <c r="C211">
         <v>957</v>
@@ -16756,7 +17475,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>132</v>
+        <v>235</v>
       </c>
       <c r="C212">
         <v>792</v>
@@ -16830,7 +17549,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>133</v>
+        <v>236</v>
       </c>
       <c r="C213">
         <v>504</v>
@@ -16904,7 +17623,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>134</v>
+        <v>237</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -16978,7 +17697,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>135</v>
+        <v>238</v>
       </c>
       <c r="C215">
         <v>549</v>
@@ -17052,7 +17771,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>136</v>
+        <v>239</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -17126,7 +17845,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>137</v>
+        <v>240</v>
       </c>
       <c r="C217">
         <v>820</v>
@@ -17200,7 +17919,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>100</v>
+        <v>241</v>
       </c>
       <c r="C218">
         <v>1006</v>
@@ -17274,7 +17993,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="C219">
         <v>1214</v>
@@ -17348,7 +18067,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>138</v>
+        <v>243</v>
       </c>
       <c r="C220">
         <v>1243</v>
@@ -17422,7 +18141,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>139</v>
+        <v>244</v>
       </c>
       <c r="C221">
         <v>1094</v>
@@ -17496,7 +18215,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>140</v>
+        <v>245</v>
       </c>
       <c r="C222">
         <v>479</v>
@@ -17570,7 +18289,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>141</v>
+        <v>246</v>
       </c>
       <c r="C223">
         <v>1102</v>
@@ -17644,7 +18363,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>142</v>
+        <v>247</v>
       </c>
       <c r="C224">
         <v>1189</v>
@@ -17718,7 +18437,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>143</v>
+        <v>248</v>
       </c>
       <c r="C225">
         <v>943</v>
@@ -17792,7 +18511,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>144</v>
+        <v>249</v>
       </c>
       <c r="C226">
         <v>1016</v>
@@ -17866,7 +18585,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -17940,7 +18659,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>146</v>
+        <v>251</v>
       </c>
       <c r="C228">
         <v>771</v>
@@ -18014,7 +18733,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>94</v>
+        <v>252</v>
       </c>
       <c r="C229">
         <v>1134</v>
@@ -18088,7 +18807,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>125</v>
+        <v>253</v>
       </c>
       <c r="C230">
         <v>1099</v>
@@ -18162,7 +18881,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -18236,7 +18955,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>148</v>
+        <v>255</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -18310,7 +19029,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="C233">
         <v>761</v>
@@ -18384,7 +19103,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>149</v>
+        <v>257</v>
       </c>
       <c r="C234">
         <v>960</v>
@@ -18458,7 +19177,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="C235">
         <v>479</v>
@@ -18532,7 +19251,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>149</v>
+        <v>259</v>
       </c>
       <c r="C236">
         <v>818</v>
@@ -18606,7 +19325,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="C237">
         <v>153</v>
@@ -18680,7 +19399,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>87</v>
+        <v>261</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -18754,7 +19473,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>148</v>
+        <v>262</v>
       </c>
       <c r="C239">
         <v>903</v>
@@ -18828,7 +19547,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="C240">
         <v>677</v>
@@ -18902,7 +19621,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>98</v>
+        <v>264</v>
       </c>
       <c r="C241">
         <v>816</v>
@@ -18976,7 +19695,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>98</v>
+        <v>265</v>
       </c>
       <c r="C242">
         <v>727</v>
@@ -19050,7 +19769,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>152</v>
+        <v>266</v>
       </c>
       <c r="C243">
         <v>789</v>
@@ -19124,7 +19843,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>153</v>
+        <v>267</v>
       </c>
       <c r="C244">
         <v>902</v>
@@ -19198,7 +19917,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>120</v>
+        <v>268</v>
       </c>
       <c r="C245">
         <v>1053</v>
@@ -19272,7 +19991,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>38</v>
+        <v>269</v>
       </c>
       <c r="C246">
         <v>549</v>
@@ -19346,7 +20065,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>34</v>
+        <v>270</v>
       </c>
       <c r="C247">
         <v>730</v>
@@ -19420,7 +20139,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>154</v>
+        <v>271</v>
       </c>
       <c r="C248">
         <v>700</v>
@@ -19494,7 +20213,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>22</v>
+        <v>272</v>
       </c>
       <c r="C249">
         <v>675</v>
@@ -19568,7 +20287,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>155</v>
+        <v>273</v>
       </c>
       <c r="C250">
         <v>680</v>
@@ -19642,7 +20361,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>25</v>
+        <v>274</v>
       </c>
       <c r="C251">
         <v>645</v>
@@ -19716,7 +20435,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>35</v>
+        <v>275</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -19790,7 +20509,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>20</v>
+        <v>276</v>
       </c>
       <c r="C253">
         <v>792</v>
@@ -19864,7 +20583,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>34</v>
+        <v>277</v>
       </c>
       <c r="C254">
         <v>1104</v>
@@ -19938,7 +20657,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>38</v>
+        <v>278</v>
       </c>
       <c r="C255">
         <v>1213</v>
@@ -20012,7 +20731,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>40</v>
+        <v>279</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -20086,7 +20805,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>38</v>
+        <v>280</v>
       </c>
       <c r="C257">
         <v>811</v>
@@ -20160,7 +20879,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>24</v>
+        <v>281</v>
       </c>
       <c r="C258">
         <v>767</v>
@@ -20234,7 +20953,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>156</v>
+        <v>282</v>
       </c>
       <c r="C259">
         <v>545</v>
@@ -20308,7 +21027,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>157</v>
+        <v>283</v>
       </c>
       <c r="C260">
         <v>951</v>
@@ -20382,7 +21101,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>158</v>
+        <v>284</v>
       </c>
       <c r="C261">
         <v>1214</v>
@@ -20456,7 +21175,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>159</v>
+        <v>285</v>
       </c>
       <c r="C262">
         <v>922</v>
@@ -20530,7 +21249,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>160</v>
+        <v>286</v>
       </c>
       <c r="C263">
         <v>1097</v>
@@ -20604,7 +21323,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>161</v>
+        <v>287</v>
       </c>
       <c r="C264">
         <v>933</v>
@@ -20678,7 +21397,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>162</v>
+        <v>288</v>
       </c>
       <c r="C265">
         <v>979</v>
@@ -20752,7 +21471,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>61</v>
+        <v>289</v>
       </c>
       <c r="C266">
         <v>755</v>
@@ -20826,7 +21545,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>25</v>
+        <v>290</v>
       </c>
       <c r="C267">
         <v>803</v>
@@ -20900,7 +21619,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>38</v>
+        <v>291</v>
       </c>
       <c r="C268">
         <v>563</v>
@@ -20974,7 +21693,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>163</v>
+        <v>292</v>
       </c>
       <c r="C269">
         <v>1192</v>
@@ -21048,7 +21767,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>163</v>
+        <v>293</v>
       </c>
       <c r="C270">
         <v>1054</v>
@@ -21122,7 +21841,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>22</v>
+        <v>294</v>
       </c>
       <c r="C271">
         <v>656</v>
@@ -21196,7 +21915,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>164</v>
+        <v>295</v>
       </c>
       <c r="C272">
         <v>626</v>
@@ -21270,7 +21989,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="C273">
         <v>1026</v>
@@ -21344,7 +22063,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>165</v>
+        <v>297</v>
       </c>
       <c r="C274">
         <v>805</v>
@@ -21418,7 +22137,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>166</v>
+        <v>298</v>
       </c>
       <c r="C275">
         <v>644</v>
@@ -21492,7 +22211,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>25</v>
+        <v>299</v>
       </c>
       <c r="C276">
         <v>977</v>
@@ -21566,7 +22285,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>25</v>
+        <v>300</v>
       </c>
       <c r="C277">
         <v>506</v>
@@ -21640,7 +22359,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>34</v>
+        <v>301</v>
       </c>
       <c r="C278">
         <v>693</v>
@@ -21714,7 +22433,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>167</v>
+        <v>302</v>
       </c>
       <c r="C279">
         <v>689</v>
@@ -21788,7 +22507,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>168</v>
+        <v>303</v>
       </c>
       <c r="C280">
         <v>748</v>
@@ -21862,7 +22581,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>169</v>
+        <v>304</v>
       </c>
       <c r="C281">
         <v>743</v>
@@ -21936,7 +22655,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>24</v>
+        <v>305</v>
       </c>
       <c r="C282">
         <v>799</v>
@@ -22010,7 +22729,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>37</v>
+        <v>306</v>
       </c>
       <c r="C283">
         <v>796</v>
@@ -22084,7 +22803,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>36</v>
+        <v>307</v>
       </c>
       <c r="C284">
         <v>720</v>
@@ -22158,7 +22877,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>40</v>
+        <v>308</v>
       </c>
       <c r="C285">
         <v>731</v>
@@ -22232,7 +22951,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>39</v>
+        <v>309</v>
       </c>
       <c r="C286">
         <v>687</v>
@@ -22306,7 +23025,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>25</v>
+        <v>310</v>
       </c>
       <c r="C287">
         <v>0</v>
@@ -22380,7 +23099,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>25</v>
+        <v>311</v>
       </c>
       <c r="C288">
         <v>1011</v>
@@ -22454,7 +23173,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>24</v>
+        <v>312</v>
       </c>
       <c r="C289">
         <v>1065</v>
@@ -22528,7 +23247,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>170</v>
+        <v>313</v>
       </c>
       <c r="C290">
         <v>502</v>
@@ -22602,7 +23321,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>171</v>
+        <v>314</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -22676,7 +23395,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>170</v>
+        <v>315</v>
       </c>
       <c r="C292">
         <v>675</v>
@@ -22750,7 +23469,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>172</v>
+        <v>316</v>
       </c>
       <c r="C293">
         <v>1118</v>
@@ -22824,7 +23543,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>25</v>
+        <v>317</v>
       </c>
       <c r="C294">
         <v>1154</v>
@@ -22898,7 +23617,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>34</v>
+        <v>318</v>
       </c>
       <c r="C295">
         <v>531</v>
@@ -22972,7 +23691,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>173</v>
+        <v>319</v>
       </c>
       <c r="C296">
         <v>692</v>
@@ -23046,7 +23765,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>174</v>
+        <v>320</v>
       </c>
       <c r="C297">
         <v>670</v>
@@ -23120,7 +23839,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>154</v>
+        <v>321</v>
       </c>
       <c r="C298">
         <v>925</v>
@@ -23194,7 +23913,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>34</v>
+        <v>322</v>
       </c>
       <c r="C299">
         <v>979</v>
@@ -23268,7 +23987,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>175</v>
+        <v>323</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -23342,7 +24061,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>176</v>
+        <v>324</v>
       </c>
       <c r="C301">
         <v>748</v>
@@ -23416,7 +24135,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>177</v>
+        <v>325</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -23490,7 +24209,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>178</v>
+        <v>326</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -23564,7 +24283,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>24</v>
+        <v>327</v>
       </c>
       <c r="C304">
         <v>961</v>
@@ -23638,7 +24357,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>53</v>
+        <v>328</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -23712,7 +24431,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>31</v>
+        <v>329</v>
       </c>
       <c r="C306">
         <v>390</v>
@@ -23786,7 +24505,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>179</v>
+        <v>330</v>
       </c>
       <c r="C307">
         <v>474</v>
@@ -23860,7 +24579,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>180</v>
+        <v>331</v>
       </c>
       <c r="C308">
         <v>672</v>
@@ -23934,7 +24653,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>181</v>
+        <v>332</v>
       </c>
       <c r="C309">
         <v>438</v>
@@ -24008,7 +24727,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>182</v>
+        <v>333</v>
       </c>
       <c r="C310">
         <v>847</v>
@@ -24082,7 +24801,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>94</v>
+        <v>334</v>
       </c>
       <c r="C311">
         <v>0</v>
@@ -24156,7 +24875,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>149</v>
+        <v>335</v>
       </c>
       <c r="C312">
         <v>1242</v>
@@ -24230,7 +24949,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>183</v>
+        <v>336</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -24304,7 +25023,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>184</v>
+        <v>337</v>
       </c>
       <c r="C314">
         <v>1156</v>
@@ -24378,7 +25097,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>185</v>
+        <v>338</v>
       </c>
       <c r="C315">
         <v>1091</v>
@@ -24452,7 +25171,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>186</v>
+        <v>339</v>
       </c>
       <c r="C316">
         <v>979</v>
@@ -24526,7 +25245,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>187</v>
+        <v>340</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -24600,7 +25319,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>188</v>
+        <v>341</v>
       </c>
       <c r="C318">
         <v>784</v>
@@ -24674,7 +25393,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>189</v>
+        <v>342</v>
       </c>
       <c r="C319">
         <v>300</v>
@@ -24748,7 +25467,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>147</v>
+        <v>343</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -24822,7 +25541,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>190</v>
+        <v>344</v>
       </c>
       <c r="C321">
         <v>916</v>
@@ -24896,7 +25615,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>190</v>
+        <v>345</v>
       </c>
       <c r="C322">
         <v>0</v>
@@ -24970,7 +25689,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>191</v>
+        <v>346</v>
       </c>
       <c r="C323">
         <v>672</v>
@@ -25044,7 +25763,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>192</v>
+        <v>347</v>
       </c>
       <c r="C324">
         <v>702</v>
@@ -25118,7 +25837,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>193</v>
+        <v>348</v>
       </c>
       <c r="C325">
         <v>801</v>
@@ -25192,7 +25911,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>94</v>
+        <v>349</v>
       </c>
       <c r="C326">
         <v>991</v>
@@ -25266,7 +25985,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>94</v>
+        <v>350</v>
       </c>
       <c r="C327">
         <v>777</v>
@@ -25340,7 +26059,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>194</v>
+        <v>351</v>
       </c>
       <c r="C328">
         <v>561</v>
@@ -25414,7 +26133,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>126</v>
+        <v>352</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -25488,7 +26207,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>195</v>
+        <v>353</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -25562,7 +26281,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>196</v>
+        <v>354</v>
       </c>
       <c r="C331">
         <v>765</v>
@@ -25636,7 +26355,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>148</v>
+        <v>355</v>
       </c>
       <c r="C332">
         <v>682</v>
@@ -25710,7 +26429,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>140</v>
+        <v>356</v>
       </c>
       <c r="C333">
         <v>1138</v>
@@ -25784,7 +26503,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>140</v>
+        <v>357</v>
       </c>
       <c r="C334">
         <v>990</v>
@@ -25858,7 +26577,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>94</v>
+        <v>358</v>
       </c>
       <c r="C335">
         <v>341</v>
@@ -25932,7 +26651,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>148</v>
+        <v>359</v>
       </c>
       <c r="C336">
         <v>972</v>
@@ -26006,7 +26725,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>120</v>
+        <v>360</v>
       </c>
       <c r="C337">
         <v>1100</v>
@@ -26080,7 +26799,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>149</v>
+        <v>361</v>
       </c>
       <c r="C338">
         <v>1052</v>
@@ -26154,7 +26873,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>137</v>
+        <v>362</v>
       </c>
       <c r="C339">
         <v>383</v>
@@ -26228,7 +26947,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>137</v>
+        <v>363</v>
       </c>
       <c r="C340">
         <v>1190</v>
@@ -26302,7 +27021,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>197</v>
+        <v>364</v>
       </c>
       <c r="C341">
         <v>0</v>
@@ -26376,7 +27095,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>98</v>
+        <v>365</v>
       </c>
       <c r="C342">
         <v>1012</v>
@@ -26450,7 +27169,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>98</v>
+        <v>366</v>
       </c>
       <c r="C343">
         <v>726</v>
@@ -26524,7 +27243,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>191</v>
+        <v>367</v>
       </c>
       <c r="C344">
         <v>794</v>
@@ -26598,7 +27317,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>198</v>
+        <v>368</v>
       </c>
       <c r="C345">
         <v>942</v>
@@ -26672,7 +27391,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>199</v>
+        <v>369</v>
       </c>
       <c r="C346">
         <v>1120</v>
@@ -26746,7 +27465,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>200</v>
+        <v>370</v>
       </c>
       <c r="C347">
         <v>997</v>
@@ -26820,7 +27539,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>201</v>
+        <v>371</v>
       </c>
       <c r="C348">
         <v>1185</v>
@@ -26894,7 +27613,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>202</v>
+        <v>372</v>
       </c>
       <c r="C349">
         <v>546</v>
@@ -26968,7 +27687,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>203</v>
+        <v>373</v>
       </c>
       <c r="C350">
         <v>1140</v>
@@ -27042,7 +27761,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>204</v>
+        <v>374</v>
       </c>
       <c r="C351">
         <v>1206</v>
@@ -27116,7 +27835,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>205</v>
+        <v>375</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -27190,7 +27909,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>206</v>
+        <v>376</v>
       </c>
       <c r="C353">
         <v>420</v>
@@ -27264,7 +27983,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>207</v>
+        <v>377</v>
       </c>
       <c r="C354">
         <v>785</v>
@@ -27338,7 +28057,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>208</v>
+        <v>378</v>
       </c>
       <c r="C355">
         <v>654</v>
@@ -27412,7 +28131,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>209</v>
+        <v>379</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -27486,7 +28205,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>210</v>
+        <v>380</v>
       </c>
       <c r="C357">
         <v>779</v>
@@ -27560,7 +28279,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>148</v>
+        <v>381</v>
       </c>
       <c r="C358">
         <v>814</v>
@@ -27634,7 +28353,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>203</v>
+        <v>382</v>
       </c>
       <c r="C359">
         <v>718</v>
@@ -27708,7 +28427,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>211</v>
+        <v>383</v>
       </c>
       <c r="C360">
         <v>574</v>
@@ -27782,7 +28501,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>212</v>
+        <v>384</v>
       </c>
       <c r="C361">
         <v>1070</v>
@@ -27856,7 +28575,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>213</v>
+        <v>385</v>
       </c>
       <c r="C362">
         <v>729</v>
@@ -27930,7 +28649,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>214</v>
+        <v>386</v>
       </c>
       <c r="C363">
         <v>544</v>
@@ -28004,7 +28723,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>215</v>
+        <v>387</v>
       </c>
       <c r="C364">
         <v>689</v>
@@ -28078,7 +28797,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>96</v>
+        <v>388</v>
       </c>
       <c r="C365">
         <v>627</v>
@@ -28152,7 +28871,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>216</v>
+        <v>389</v>
       </c>
       <c r="C366">
         <v>1083</v>
@@ -28226,7 +28945,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>217</v>
+        <v>390</v>
       </c>
       <c r="C367">
         <v>1146</v>
@@ -28300,7 +29019,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>98</v>
+        <v>391</v>
       </c>
       <c r="C368">
         <v>653</v>
@@ -28374,7 +29093,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>105</v>
+        <v>392</v>
       </c>
       <c r="C369">
         <v>1110</v>
@@ -28448,7 +29167,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>218</v>
+        <v>393</v>
       </c>
       <c r="C370">
         <v>0</v>
@@ -28522,7 +29241,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>22</v>
+        <v>394</v>
       </c>
       <c r="C371">
         <v>999</v>
@@ -28596,7 +29315,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>40</v>
+        <v>395</v>
       </c>
       <c r="C372">
         <v>465</v>
@@ -28670,7 +29389,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>219</v>
+        <v>396</v>
       </c>
       <c r="C373">
         <v>711</v>
@@ -28744,7 +29463,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>40</v>
+        <v>397</v>
       </c>
       <c r="C374">
         <v>737</v>
@@ -28818,7 +29537,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>40</v>
+        <v>398</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -28892,7 +29611,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>220</v>
+        <v>399</v>
       </c>
       <c r="C376">
         <v>1130</v>
@@ -28966,7 +29685,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>221</v>
+        <v>400</v>
       </c>
       <c r="C377">
         <v>0</v>
@@ -29040,7 +29759,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>222</v>
+        <v>401</v>
       </c>
       <c r="C378">
         <v>851</v>
@@ -29114,7 +29833,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>223</v>
+        <v>402</v>
       </c>
       <c r="C379">
         <v>726</v>
@@ -29188,7 +29907,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>224</v>
+        <v>403</v>
       </c>
       <c r="C380">
         <v>454</v>
@@ -29262,7 +29981,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>24</v>
+        <v>404</v>
       </c>
       <c r="C381">
         <v>703</v>
@@ -29336,7 +30055,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>24</v>
+        <v>405</v>
       </c>
       <c r="C382">
         <v>647</v>
@@ -29410,7 +30129,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>60</v>
+        <v>406</v>
       </c>
       <c r="C383">
         <v>0</v>
@@ -29484,7 +30203,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>225</v>
+        <v>407</v>
       </c>
       <c r="C384">
         <v>1182</v>
@@ -29558,7 +30277,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>225</v>
+        <v>408</v>
       </c>
       <c r="C385">
         <v>1039</v>
@@ -29632,7 +30351,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>226</v>
+        <v>409</v>
       </c>
       <c r="C386">
         <v>1189</v>
@@ -29706,7 +30425,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>227</v>
+        <v>410</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -29780,7 +30499,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>228</v>
+        <v>411</v>
       </c>
       <c r="C388">
         <v>749</v>
@@ -29854,7 +30573,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>228</v>
+        <v>412</v>
       </c>
       <c r="C389">
         <v>1168</v>
@@ -29928,7 +30647,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>38</v>
+        <v>413</v>
       </c>
       <c r="C390">
         <v>0</v>
@@ -30002,7 +30721,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>229</v>
+        <v>414</v>
       </c>
       <c r="C391">
         <v>0</v>
@@ -30076,7 +30795,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>229</v>
+        <v>415</v>
       </c>
       <c r="C392">
         <v>1218</v>
@@ -30150,7 +30869,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>229</v>
+        <v>416</v>
       </c>
       <c r="C393">
         <v>811</v>
@@ -30224,7 +30943,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>229</v>
+        <v>417</v>
       </c>
       <c r="C394">
         <v>1143</v>
@@ -30298,7 +31017,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>229</v>
+        <v>418</v>
       </c>
       <c r="C395">
         <v>1086</v>
@@ -30372,7 +31091,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>229</v>
+        <v>419</v>
       </c>
       <c r="C396">
         <v>761</v>
@@ -30446,7 +31165,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>230</v>
+        <v>420</v>
       </c>
       <c r="C397">
         <v>1162</v>
@@ -30520,7 +31239,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>40</v>
+        <v>421</v>
       </c>
       <c r="C398">
         <v>780</v>
@@ -30594,7 +31313,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>40</v>
+        <v>422</v>
       </c>
       <c r="C399">
         <v>762</v>
@@ -30668,7 +31387,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>24</v>
+        <v>423</v>
       </c>
       <c r="C400">
         <v>769</v>
@@ -30742,7 +31461,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>231</v>
+        <v>424</v>
       </c>
       <c r="C401">
         <v>1197</v>
@@ -30816,7 +31535,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>231</v>
+        <v>425</v>
       </c>
       <c r="C402">
         <v>1185</v>
@@ -30890,7 +31609,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>231</v>
+        <v>426</v>
       </c>
       <c r="C403">
         <v>0</v>
@@ -30964,7 +31683,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>231</v>
+        <v>427</v>
       </c>
       <c r="C404">
         <v>931</v>
@@ -31038,7 +31757,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>232</v>
+        <v>428</v>
       </c>
       <c r="C405">
         <v>532</v>
@@ -31112,7 +31831,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>233</v>
+        <v>429</v>
       </c>
       <c r="C406">
         <v>1229</v>
@@ -31186,7 +31905,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>234</v>
+        <v>430</v>
       </c>
       <c r="C407">
         <v>0</v>
@@ -31260,7 +31979,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>235</v>
+        <v>431</v>
       </c>
       <c r="C408">
         <v>1115</v>
@@ -31334,7 +32053,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>236</v>
+        <v>432</v>
       </c>
       <c r="C409">
         <v>980</v>
@@ -31408,7 +32127,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>236</v>
+        <v>433</v>
       </c>
       <c r="C410">
         <v>1006</v>
@@ -31482,7 +32201,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>236</v>
+        <v>434</v>
       </c>
       <c r="C411">
         <v>894</v>
@@ -31556,7 +32275,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>236</v>
+        <v>435</v>
       </c>
       <c r="C412">
         <v>1043</v>
@@ -31630,7 +32349,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>236</v>
+        <v>436</v>
       </c>
       <c r="C413">
         <v>1028</v>
@@ -31704,7 +32423,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>237</v>
+        <v>437</v>
       </c>
       <c r="C414">
         <v>982</v>
@@ -31778,7 +32497,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>238</v>
+        <v>438</v>
       </c>
       <c r="C415">
         <v>1205</v>
@@ -31852,7 +32571,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>239</v>
+        <v>439</v>
       </c>
       <c r="C416">
         <v>1135</v>
@@ -31926,7 +32645,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>240</v>
+        <v>440</v>
       </c>
       <c r="C417">
         <v>1241</v>
@@ -32000,7 +32719,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>241</v>
+        <v>441</v>
       </c>
       <c r="C418">
         <v>1166</v>
@@ -32074,7 +32793,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>242</v>
+        <v>442</v>
       </c>
       <c r="C419">
         <v>1085</v>
@@ -32148,7 +32867,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>243</v>
+        <v>443</v>
       </c>
       <c r="C420">
         <v>1216</v>
@@ -32222,7 +32941,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>244</v>
+        <v>444</v>
       </c>
       <c r="C421">
         <v>1061</v>
@@ -32296,7 +33015,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>245</v>
+        <v>445</v>
       </c>
       <c r="C422">
         <v>1118</v>
@@ -32370,7 +33089,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>246</v>
+        <v>446</v>
       </c>
       <c r="C423">
         <v>952</v>
@@ -32444,7 +33163,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>247</v>
+        <v>447</v>
       </c>
       <c r="C424">
         <v>983</v>
@@ -32518,7 +33237,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>248</v>
+        <v>448</v>
       </c>
       <c r="C425">
         <v>907</v>
@@ -32592,7 +33311,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>249</v>
+        <v>449</v>
       </c>
       <c r="C426">
         <v>904</v>
@@ -32666,7 +33385,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="C427">
         <v>1066</v>
@@ -32740,7 +33459,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>251</v>
+        <v>451</v>
       </c>
       <c r="C428">
         <v>1048</v>
@@ -32814,7 +33533,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>252</v>
+        <v>452</v>
       </c>
       <c r="C429">
         <v>1042</v>
@@ -32888,7 +33607,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>253</v>
+        <v>453</v>
       </c>
       <c r="C430">
         <v>1031</v>
@@ -32962,7 +33681,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>254</v>
+        <v>454</v>
       </c>
       <c r="C431">
         <v>869</v>
@@ -33036,7 +33755,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>255</v>
+        <v>455</v>
       </c>
       <c r="C432">
         <v>812</v>
@@ -33110,7 +33829,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>256</v>
+        <v>456</v>
       </c>
       <c r="C433">
         <v>1213</v>
@@ -33184,7 +33903,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>256</v>
+        <v>457</v>
       </c>
       <c r="C434">
         <v>1120</v>
@@ -33258,7 +33977,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>256</v>
+        <v>458</v>
       </c>
       <c r="C435">
         <v>913</v>
@@ -33332,7 +34051,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>257</v>
+        <v>459</v>
       </c>
       <c r="C436">
         <v>964</v>
@@ -33406,7 +34125,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>258</v>
+        <v>460</v>
       </c>
       <c r="C437">
         <v>1055</v>
@@ -33480,7 +34199,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>53</v>
+        <v>461</v>
       </c>
       <c r="C438">
         <v>1155</v>
@@ -33554,7 +34273,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>259</v>
+        <v>462</v>
       </c>
       <c r="C439">
         <v>759</v>
@@ -33628,7 +34347,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>260</v>
+        <v>463</v>
       </c>
       <c r="C440">
         <v>695</v>
@@ -33702,7 +34421,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>261</v>
+        <v>464</v>
       </c>
       <c r="C441">
         <v>1149</v>
@@ -33776,7 +34495,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>262</v>
+        <v>465</v>
       </c>
       <c r="C442">
         <v>964</v>
@@ -33850,7 +34569,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>263</v>
+        <v>466</v>
       </c>
       <c r="C443">
         <v>1179</v>
@@ -33924,7 +34643,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>263</v>
+        <v>467</v>
       </c>
       <c r="C444">
         <v>1091</v>
@@ -33998,7 +34717,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>40</v>
+        <v>468</v>
       </c>
       <c r="C445">
         <v>1159</v>
@@ -34072,7 +34791,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>39</v>
+        <v>469</v>
       </c>
       <c r="C446">
         <v>1139</v>
@@ -34146,7 +34865,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>40</v>
+        <v>470</v>
       </c>
       <c r="C447">
         <v>1122</v>
@@ -34220,7 +34939,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>40</v>
+        <v>471</v>
       </c>
       <c r="C448">
         <v>1147</v>
